--- a/results/feature_selection/global_ind/wrapper/rP_calc/metrics_global.xlsx
+++ b/results/feature_selection/global_ind/wrapper/rP_calc/metrics_global.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>tweedie</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -496,77 +496,77 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>t, t_ind_ad, P, I, Plag1</t>
+          <t>t_ind, t_ind_ad, I, X_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9448809657494204</v>
+        <v>0.8640981665468496</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03154782873008918</v>
+        <v>0.04750401435142174</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002444921028484018</v>
+        <v>0.006028212484794147</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04944614270581698</v>
+        <v>0.07764156415731298</v>
       </c>
       <c r="H2" t="n">
-        <v>332.9247639263567</v>
+        <v>774.4886734439743</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0207471549951127</v>
+        <v>0.04749029877530105</v>
       </c>
       <c r="J2" t="n">
-        <v>-314.7420926113355</v>
+        <v>-266.0104564570741</v>
       </c>
       <c r="K2" t="n">
-        <v>-304.7971723785141</v>
+        <v>-256.0655362242527</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>poisson</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>t_ind, t_ind_ad, I, X_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9092486495346642</v>
+        <v>0.8595092124156538</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0364799641240915</v>
+        <v>0.046545284573362</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00402546757454643</v>
+        <v>0.006231765224907533</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06344657259889167</v>
+        <v>0.07894153041908633</v>
       </c>
       <c r="H3" t="n">
-        <v>187.9066402806145</v>
+        <v>657.4089207386717</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03104323244178324</v>
+        <v>0.04850947193273913</v>
       </c>
       <c r="J3" t="n">
-        <v>-293.8161671925458</v>
+        <v>-266.217164756287</v>
       </c>
       <c r="K3" t="n">
-        <v>-289.8381990994173</v>
+        <v>-258.2612285700299</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ridge_b</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -574,38 +574,38 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>t, P, Plag1</t>
+          <t>t, t_ind_ad, V_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9047906560293142</v>
+        <v>0.7384451602908944</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0388946603151017</v>
+        <v>0.05121666835162998</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004223211279861094</v>
+        <v>0.01160181662108556</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06498623915769472</v>
+        <v>0.1077117292642058</v>
       </c>
       <c r="H4" t="n">
-        <v>314.7652880675732</v>
+        <v>810.2733315750281</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03301905108710852</v>
+        <v>0.0880877235474916</v>
       </c>
       <c r="J4" t="n">
-        <v>-289.2266115706695</v>
+        <v>-234.6560537447179</v>
       </c>
       <c r="K4" t="n">
-        <v>-283.2596594309767</v>
+        <v>-228.689101605025</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>elasticnet_b</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -613,38 +613,38 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>t, P, Plag1</t>
+          <t>t, t_ind_ad, V_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9033033570950676</v>
+        <v>0.6164814465528267</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03913524746691281</v>
+        <v>0.06859742982487851</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004289183561295672</v>
+        <v>0.0170117744058062</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06549185874057685</v>
+        <v>0.1304291930735071</v>
       </c>
       <c r="H5" t="n">
-        <v>321.8619781513881</v>
+        <v>2051.73731143862</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0335114213643867</v>
+        <v>0.1284638081182164</v>
       </c>
       <c r="J5" t="n">
-        <v>-288.3895793151315</v>
+        <v>-213.9878763784962</v>
       </c>
       <c r="K5" t="n">
-        <v>-282.4226271754387</v>
+        <v>-208.0209242388034</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LASSO_b</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -652,116 +652,116 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>t, P, Plag1</t>
+          <t>t_ind_ad, T, V_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.896378492896259</v>
+        <v>0.4732329489943214</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04006381204733326</v>
+        <v>0.06157562063875881</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004596350519666051</v>
+        <v>0.0233658636735413</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06779639016692593</v>
+        <v>0.1528589666115184</v>
       </c>
       <c r="H6" t="n">
-        <v>344.4526477466405</v>
+        <v>649.4143231817164</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03580389749488853</v>
+        <v>0.1758862198731825</v>
       </c>
       <c r="J6" t="n">
-        <v>-284.6546034055252</v>
+        <v>-196.8498735113225</v>
       </c>
       <c r="K6" t="n">
-        <v>-278.6876512658324</v>
+        <v>-190.8829213716296</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tweedie</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P, I, FS_calc, Plag1, X_calc, V_calc, mu_calc, dVdt_calc</t>
+          <t>t_ind, t_ind_ad, V_calc, mu_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8661789907974714</v>
+        <v>0.3308037940461492</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0438049626062479</v>
+        <v>0.0889075659315146</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00593591313601027</v>
+        <v>0.02968360927153012</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07704487741576509</v>
+        <v>0.1722893185067784</v>
       </c>
       <c r="H7" t="n">
-        <v>328.8223979909214</v>
+        <v>1578.570628410999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04830144195596577</v>
+        <v>0.2240373882762264</v>
       </c>
       <c r="J7" t="n">
-        <v>-260.8436579588612</v>
+        <v>-179.9266541422091</v>
       </c>
       <c r="K7" t="n">
-        <v>-244.931785586347</v>
+        <v>-169.9817339093877</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>poisson</t>
+          <t>LASSO_b</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>t, t_ind_ad, P, T, I, Plag1, X_calc, V_calc, mu_calc, dVdt_calc, Xlag1_calc</t>
+          <t>t, t_ind, t_ind_ad, X_calc, V_calc, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8324974551593122</v>
+        <v>0.2782559221509029</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04678215528314972</v>
+        <v>0.08503606133365596</v>
       </c>
       <c r="F8" t="n">
-        <v>0.007429928694755357</v>
+        <v>0.03201448097031032</v>
       </c>
       <c r="G8" t="n">
-        <v>0.08619703414129373</v>
+        <v>0.1789259091644089</v>
       </c>
       <c r="H8" t="n">
-        <v>623.7675566933121</v>
+        <v>1466.938510878346</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0609517135385351</v>
+        <v>0.2424333600339464</v>
       </c>
       <c r="J8" t="n">
-        <v>-242.720906930738</v>
+        <v>-171.8446152039437</v>
       </c>
       <c r="K8" t="n">
-        <v>-220.8420824185309</v>
+        <v>-157.9217268779938</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>Ridge_b</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -769,110 +769,110 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7495500543634079</v>
+        <v>0.1350336228305058</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05974742181461012</v>
+        <v>0.08618739164752932</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0111092356205995</v>
+        <v>0.03836740815993336</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1054003587308862</v>
+        <v>0.195876002001096</v>
       </c>
       <c r="H9" t="n">
-        <v>153.9998773539669</v>
+        <v>975.280090340925</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08391144862539728</v>
+        <v>0.2873470988628016</v>
       </c>
       <c r="J9" t="n">
-        <v>-238.9988378510768</v>
+        <v>-172.069533983059</v>
       </c>
       <c r="K9" t="n">
-        <v>-235.0208697579483</v>
+        <v>-168.0915658899305</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rf_b</t>
+          <t>elasticnet_b</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7435866014850534</v>
+        <v>0.1345005100572852</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06287713904046242</v>
+        <v>0.08618720856688357</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01137375715191623</v>
+        <v>0.03839105550150097</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1066478183176582</v>
+        <v>0.1959363557421158</v>
       </c>
       <c r="H10" t="n">
-        <v>935.7441250929817</v>
+        <v>974.9819521270477</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08538564956082535</v>
+        <v>0.2875235858338651</v>
       </c>
       <c r="J10" t="n">
-        <v>-239.7281154001675</v>
+        <v>-172.0362619131363</v>
       </c>
       <c r="K10" t="n">
-        <v>-237.7391313536032</v>
+        <v>-168.0582938200078</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>rf_b</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>t, t_ind, t_ind_ad, T, mu_calc</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.7393072517262287</v>
+        <v>0.08429525171871266</v>
       </c>
       <c r="E11" t="n">
-        <v>0.06964476722318771</v>
+        <v>0.0892599458571684</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01156357673703493</v>
+        <v>0.040618015634627</v>
       </c>
       <c r="G11" t="n">
-        <v>0.107534072446992</v>
+        <v>0.2015391168846063</v>
       </c>
       <c r="H11" t="n">
-        <v>1017.313203392419</v>
+        <v>1103.494280478879</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08680232819805585</v>
+        <v>0.3056440354286251</v>
       </c>
       <c r="J11" t="n">
-        <v>-238.8343330929185</v>
+        <v>-162.991353101441</v>
       </c>
       <c r="K11" t="n">
-        <v>-236.8453490463542</v>
+        <v>-153.0464328686197</v>
       </c>
     </row>
     <row r="12">
@@ -886,32 +886,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.7066864085453262</v>
+        <v>-0.1287744366031316</v>
       </c>
       <c r="E12" t="n">
-        <v>0.07092384994669788</v>
+        <v>0.1291494678080648</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01301054304448669</v>
+        <v>0.05006917109468723</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1140637674482423</v>
+        <v>0.2237614155628428</v>
       </c>
       <c r="H12" t="n">
-        <v>1387.728476180631</v>
+        <v>1978.616395929415</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09760145756754285</v>
+        <v>0.7483615014944413</v>
       </c>
       <c r="J12" t="n">
-        <v>-232.4677433263427</v>
+        <v>-159.6948896161603</v>
       </c>
       <c r="K12" t="n">
-        <v>-230.4787592797784</v>
+        <v>-157.705905569596</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global_ind/wrapper/rP_calc/metrics_global.xlsx
+++ b/results/feature_selection/global_ind/wrapper/rP_calc/metrics_global.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tweedie</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -496,32 +496,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, I, X_calc, Xlag1_calc</t>
+          <t>t, t_ind_ad, T, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.8640981665468496</v>
+        <v>0.7333261517090193</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04750401435142174</v>
+        <v>0.05295335408539856</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006028212484794147</v>
+        <v>0.01182888104441924</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07764156415731298</v>
+        <v>0.1087606594519325</v>
       </c>
       <c r="H2" t="n">
-        <v>774.4886734439743</v>
+        <v>543.2581721695417</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04749029877530105</v>
+        <v>0.0907823712183877</v>
       </c>
       <c r="J2" t="n">
-        <v>-266.0104564570741</v>
+        <v>-229.6094043537423</v>
       </c>
       <c r="K2" t="n">
-        <v>-256.0655362242527</v>
+        <v>-219.6644841209209</v>
       </c>
     </row>
     <row r="3">
@@ -531,114 +531,114 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, I, X_calc</t>
+          <t>t, t_ind_ad, I, FS_calc, X_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8595092124156538</v>
+        <v>0.6734816108733199</v>
       </c>
       <c r="E3" t="n">
-        <v>0.046545284573362</v>
+        <v>0.05673780865978423</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006231765224907533</v>
+        <v>0.01448341188514479</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07894153041908633</v>
+        <v>0.1203470476793876</v>
       </c>
       <c r="H3" t="n">
-        <v>657.4089207386717</v>
+        <v>805.4534428522485</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04850947193273913</v>
+        <v>0.1105939050576054</v>
       </c>
       <c r="J3" t="n">
-        <v>-266.217164756287</v>
+        <v>-218.676569787074</v>
       </c>
       <c r="K3" t="n">
-        <v>-258.2612285700299</v>
+        <v>-208.7316495542526</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>t, t_ind_ad, V_calc</t>
+          <t>t, t_ind_ad, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7384451602908944</v>
+        <v>0.6579917381234551</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05121666835162998</v>
+        <v>0.06807995459378995</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01160181662108556</v>
+        <v>0.01517049786423717</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1077117292642058</v>
+        <v>0.1231685749866303</v>
       </c>
       <c r="H4" t="n">
-        <v>810.2733315750281</v>
+        <v>1684.234000898572</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0880877235474916</v>
+        <v>0.1152218270679295</v>
       </c>
       <c r="J4" t="n">
-        <v>-234.6560537447179</v>
+        <v>-218.1737440266268</v>
       </c>
       <c r="K4" t="n">
-        <v>-228.689101605025</v>
+        <v>-210.2178078403697</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>tweedie</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>t, t_ind_ad, V_calc</t>
+          <t>t, t_ind_ad, I, FS_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.6164814465528267</v>
+        <v>0.6474949713661606</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06859742982487851</v>
+        <v>0.06835999391480167</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0170117744058062</v>
+        <v>0.01563610409491476</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1304291930735071</v>
+        <v>0.1250444084912027</v>
       </c>
       <c r="H5" t="n">
-        <v>2051.73731143862</v>
+        <v>1800.34518956025</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1284638081182164</v>
+        <v>0.1191967814565922</v>
       </c>
       <c r="J5" t="n">
-        <v>-213.9878763784962</v>
+        <v>-214.5413243790356</v>
       </c>
       <c r="K5" t="n">
-        <v>-208.0209242388034</v>
+        <v>-204.5964041462143</v>
       </c>
     </row>
     <row r="6">
@@ -691,32 +691,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, V_calc, mu_calc, Xlag1_calc</t>
+          <t>t, t_ind_ad, T, V_calc, mu_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3308037940461492</v>
+        <v>0.348618307038443</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0889075659315146</v>
+        <v>0.0884552902304382</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02968360927153012</v>
+        <v>0.02889340897104858</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1722893185067784</v>
+        <v>0.1699806135153317</v>
       </c>
       <c r="H7" t="n">
-        <v>1578.570628410999</v>
+        <v>1684.714055593055</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2240373882762264</v>
+        <v>0.2181398941682011</v>
       </c>
       <c r="J7" t="n">
-        <v>-179.9266541422091</v>
+        <v>-181.3836557506213</v>
       </c>
       <c r="K7" t="n">
-        <v>-169.9817339093877</v>
+        <v>-171.4387355177999</v>
       </c>
     </row>
     <row r="8">
@@ -726,36 +726,36 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, X_calc, V_calc, mu_calc, dXdt_calc</t>
+          <t>t, t_ind_ad, X_calc, V_calc, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2782559221509029</v>
+        <v>0.2597702571769724</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08503606133365596</v>
+        <v>0.08848175403120651</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03201448097031032</v>
+        <v>0.03283445163261919</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1789259091644089</v>
+        <v>0.1812027914592355</v>
       </c>
       <c r="H8" t="n">
-        <v>1466.938510878346</v>
+        <v>1525.416067621669</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2424333600339464</v>
+        <v>0.2480530389897417</v>
       </c>
       <c r="J8" t="n">
-        <v>-171.8446152039437</v>
+        <v>-172.4789558494771</v>
       </c>
       <c r="K8" t="n">
-        <v>-157.9217268779938</v>
+        <v>-160.5450515700914</v>
       </c>
     </row>
     <row r="9">
@@ -843,36 +843,36 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, T, mu_calc</t>
+          <t>t, t_ind_ad, T, V_calc, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.08429525171871266</v>
+        <v>0.08157907969562361</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0892599458571684</v>
+        <v>0.09033521887128308</v>
       </c>
       <c r="F11" t="n">
-        <v>0.040618015634627</v>
+        <v>0.04073849717401755</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2015391168846063</v>
+        <v>0.2018377991705655</v>
       </c>
       <c r="H11" t="n">
-        <v>1103.494280478879</v>
+        <v>1029.317777170362</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3056440354286251</v>
+        <v>0.3070432241131252</v>
       </c>
       <c r="J11" t="n">
-        <v>-162.991353101441</v>
+        <v>-160.8314148823957</v>
       </c>
       <c r="K11" t="n">
-        <v>-153.0464328686197</v>
+        <v>-148.89751060301</v>
       </c>
     </row>
     <row r="12">
